--- a/artfynd/A 22287-2023 artfynd.xlsx
+++ b/artfynd/A 22287-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 22287-2023 artfynd.xlsx
+++ b/artfynd/A 22287-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6773600</v>
+        <v>6766641</v>
       </c>
       <c r="B2" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>162</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>682714.5028605335</v>
+        <v>682710</v>
       </c>
       <c r="R2" t="n">
-        <v>6694375.475537388</v>
+        <v>6694360</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,27 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2000-06-25</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-06-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2000-06-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-06-14</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>40 ex (med 7 klockor)</t>
+          <t>162 ex (102 blr)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,15 +790,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6766641</v>
+        <v>6773600</v>
       </c>
       <c r="B3" t="n">
-        <v>96239</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,7 +820,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -854,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>682709.7992698627</v>
+        <v>682715</v>
       </c>
       <c r="R3" t="n">
-        <v>6694360.363486546</v>
+        <v>6694375</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,27 +864,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2007-06-14</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-06-25</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2007-06-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2000-06-25</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>162 ex (102 blr)</t>
+          <t>40 ex (med 7 klockor)</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,6 +900,411 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Floraväkteri C-län</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>75541620</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99024</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>504</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Guckusko</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Cypripedium calceolus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Stenfjärden, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>682909</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6694283</v>
+      </c>
+      <c r="S4" t="n">
+        <v>15</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2018-09-19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2018-09-19</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Maria Jakobsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Maria Jakobsson, Olle Finnström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>111957093</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91680</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>3215</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Rödgul trumpetsvamp</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Craterellus lutescens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Stenfjärden SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>682884</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6694208</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>111943999</v>
+      </c>
+      <c r="B6" t="n">
+        <v>102241</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Stenfjärden SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>682757</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6694406</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>111943998</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stenfjärden SV, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>682757</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6694406</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Börstil</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-09-05</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Karin Wiklund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
     </row>

--- a/artfynd/A 22287-2023 artfynd.xlsx
+++ b/artfynd/A 22287-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Floraväkteri C-län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6766641</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Floraväkteri C-län</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6773600</t>
         </is>
       </c>
     </row>
@@ -1004,6 +1019,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75541620</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111957093</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1206,6 +1231,11 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111943999</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1307,8 +1337,21 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111943998</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>